--- a/i18n/jp.xlsx
+++ b/i18n/jp.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-21690" yWindow="-105" windowWidth="21795" windowHeight="12975"/>
+    <workbookView xWindow="-21690" yWindow="-105" windowWidth="21795" windowHeight="12975" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -3572,144 +3572,9 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Birds Cards in Hand</t>
   </si>
   <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>No Goal</t>
-  </si>
-  <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
-  </si>
-  <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
-    <t>In Forest</t>
-  </si>
-  <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
-    <t>Total Duet Tokens</t>
-  </si>
-  <si>
     <t>Translated</t>
   </si>
   <si>
@@ -3801,6 +3666,141 @@
   </si>
   <si>
     <t>Flavor text</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
   </si>
 </sst>
 </file>
@@ -3821,28 +3821,37 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3872,7 +3881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3894,6 +3903,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4141,7 +4151,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>1255</v>
+        <v>1210</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -4770,7 +4780,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1246</v>
+        <v>1201</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>78</v>
@@ -6132,7 +6142,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>1247</v>
+        <v>1202</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>221</v>
@@ -6757,7 +6767,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>286</v>
@@ -7504,7 +7514,7 @@
         <v>365</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1250</v>
+        <v>1205</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>13</v>
@@ -9763,7 +9773,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="11" t="s">
-        <v>1252</v>
+        <v>1207</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>603</v>
@@ -10018,7 +10028,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>1248</v>
+        <v>1203</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>630</v>
@@ -11192,7 +11202,7 @@
         <v>773</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>1254</v>
+        <v>1209</v>
       </c>
       <c r="G370" s="1"/>
       <c r="H370" s="1"/>
@@ -11262,7 +11272,7 @@
         <v>784</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>1253</v>
+        <v>1208</v>
       </c>
       <c r="G373" s="1"/>
       <c r="H373" s="1"/>
@@ -11873,7 +11883,7 @@
         <v>885</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1251</v>
+        <v>1206</v>
       </c>
       <c r="D399" s="2" t="s">
         <v>723</v>
@@ -19266,7 +19276,7 @@
         <v>1132</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>1245</v>
+        <v>1200</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
@@ -29058,8 +29068,8 @@
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>1179</v>
+      <c r="B2" s="13" t="s">
+        <v>1211</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>13</v>
@@ -29072,8 +29082,8 @@
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>1180</v>
+      <c r="B3" s="13" t="s">
+        <v>1212</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>13</v>
@@ -29086,8 +29096,8 @@
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>1181</v>
+      <c r="B4" s="13" t="s">
+        <v>1213</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>13</v>
@@ -29100,8 +29110,8 @@
       <c r="A5" s="7">
         <v>2013</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>1182</v>
+      <c r="B5" s="13" t="s">
+        <v>1214</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -29114,8 +29124,8 @@
       <c r="A6" s="7">
         <v>2014</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>1183</v>
+      <c r="B6" s="13" t="s">
+        <v>1215</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>13</v>
@@ -29128,8 +29138,8 @@
       <c r="A7" s="7">
         <v>2017</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>1184</v>
+      <c r="B7" s="13" t="s">
+        <v>1216</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
@@ -29142,8 +29152,8 @@
       <c r="A8" s="7">
         <v>2010</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>1185</v>
+      <c r="B8" s="13" t="s">
+        <v>1217</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>13</v>
@@ -29156,8 +29166,8 @@
       <c r="A9" s="7">
         <v>2008</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>1186</v>
+      <c r="B9" s="13" t="s">
+        <v>1218</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>13</v>
@@ -29170,8 +29180,8 @@
       <c r="A10" s="7">
         <v>2021</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>1187</v>
+      <c r="B10" s="13" t="s">
+        <v>1219</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>13</v>
@@ -29184,8 +29194,8 @@
       <c r="A11" s="7">
         <v>2022</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>1188</v>
+      <c r="B11" s="13" t="s">
+        <v>1220</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>13</v>
@@ -29198,8 +29208,8 @@
       <c r="A12" s="7">
         <v>2012</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>1189</v>
+      <c r="B12" s="13" t="s">
+        <v>1221</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>13</v>
@@ -29212,8 +29222,8 @@
       <c r="A13" s="7">
         <v>2011</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>1190</v>
+      <c r="B13" s="13" t="s">
+        <v>1222</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>13</v>
@@ -29226,8 +29236,8 @@
       <c r="A14" s="7">
         <v>2015</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>1191</v>
+      <c r="B14" s="13" t="s">
+        <v>1223</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>13</v>
@@ -29240,8 +29250,8 @@
       <c r="A15" s="7">
         <v>2016</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>1192</v>
+      <c r="B15" s="13" t="s">
+        <v>1224</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>13</v>
@@ -29254,8 +29264,8 @@
       <c r="A16" s="7">
         <v>2023</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>1193</v>
+      <c r="B16" s="13" t="s">
+        <v>1225</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>13</v>
@@ -29268,8 +29278,8 @@
       <c r="A17" s="7">
         <v>2024</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>1194</v>
+      <c r="B17" s="13" t="s">
+        <v>1226</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>13</v>
@@ -29282,8 +29292,8 @@
       <c r="A18" s="7">
         <v>2020</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>1195</v>
+      <c r="B18" s="13" t="s">
+        <v>1227</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>47</v>
@@ -29296,8 +29306,8 @@
       <c r="A19" s="1">
         <v>2003</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>1196</v>
+      <c r="B19" s="13" t="s">
+        <v>1179</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>47</v>
@@ -29310,8 +29320,8 @@
       <c r="A20" s="7">
         <v>2004</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>1197</v>
+      <c r="B20" s="13" t="s">
+        <v>1228</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>47</v>
@@ -29324,8 +29334,8 @@
       <c r="A21" s="7">
         <v>2006</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>1198</v>
+      <c r="B21" s="13" t="s">
+        <v>1229</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>47</v>
@@ -29338,8 +29348,8 @@
       <c r="A22" s="7">
         <v>2005</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>1199</v>
+      <c r="B22" s="13" t="s">
+        <v>1230</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>47</v>
@@ -29352,8 +29362,8 @@
       <c r="A23" s="7">
         <v>2018</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>1200</v>
+      <c r="B23" s="13" t="s">
+        <v>1231</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>47</v>
@@ -29366,8 +29376,8 @@
       <c r="A24" s="7">
         <v>2009</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>1201</v>
+      <c r="B24" s="13" t="s">
+        <v>1232</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>47</v>
@@ -29380,8 +29390,8 @@
       <c r="A25" s="7">
         <v>2025</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>1202</v>
+      <c r="B25" s="13" t="s">
+        <v>1233</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>47</v>
@@ -29394,8 +29404,8 @@
       <c r="A26" s="7">
         <v>2007</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>1203</v>
+      <c r="B26" s="13" t="s">
+        <v>1234</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>47</v>
@@ -29408,8 +29418,8 @@
       <c r="A27" s="7">
         <v>2019</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>1204</v>
+      <c r="B27" s="13" t="s">
+        <v>1235</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>47</v>
@@ -29422,8 +29432,8 @@
       <c r="A28" s="7">
         <v>2031</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>1205</v>
+      <c r="B28" s="13" t="s">
+        <v>1236</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>534</v>
@@ -29436,8 +29446,8 @@
       <c r="A29" s="7">
         <v>2030</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>1206</v>
+      <c r="B29" s="13" t="s">
+        <v>1237</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>534</v>
@@ -29450,8 +29460,8 @@
       <c r="A30" s="7">
         <v>2033</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>1207</v>
+      <c r="B30" s="13" t="s">
+        <v>1238</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>534</v>
@@ -29464,8 +29474,8 @@
       <c r="A31" s="7">
         <v>2032</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>1208</v>
+      <c r="B31" s="13" t="s">
+        <v>1239</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>534</v>
@@ -29478,8 +29488,8 @@
       <c r="A32" s="7">
         <v>2026</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>1209</v>
+      <c r="B32" s="13" t="s">
+        <v>1240</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>534</v>
@@ -29492,8 +29502,8 @@
       <c r="A33" s="7">
         <v>2027</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>1210</v>
+      <c r="B33" s="13" t="s">
+        <v>1241</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>534</v>
@@ -29506,8 +29516,8 @@
       <c r="A34" s="7">
         <v>2029</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>1211</v>
+      <c r="B34" s="13" t="s">
+        <v>1242</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>534</v>
@@ -29520,8 +29530,8 @@
       <c r="A35" s="7">
         <v>2028</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>1212</v>
+      <c r="B35" s="13" t="s">
+        <v>1243</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>534</v>
@@ -29534,8 +29544,8 @@
       <c r="A36" s="7">
         <v>2043</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>1213</v>
+      <c r="B36" s="1" t="s">
+        <v>1244</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>723</v>
@@ -29548,8 +29558,8 @@
       <c r="A37" s="7">
         <v>2040</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>1214</v>
+      <c r="B37" s="13" t="s">
+        <v>1245</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>723</v>
@@ -29562,8 +29572,8 @@
       <c r="A38" s="7">
         <v>2035</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>1215</v>
+      <c r="B38" s="13" t="s">
+        <v>1246</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>723</v>
@@ -29576,8 +29586,8 @@
       <c r="A39" s="7">
         <v>2041</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>1216</v>
+      <c r="B39" s="13" t="s">
+        <v>1247</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>723</v>
@@ -29590,8 +29600,8 @@
       <c r="A40" s="7">
         <v>2042</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>1217</v>
+      <c r="B40" s="13" t="s">
+        <v>1248</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>723</v>
@@ -29604,8 +29614,8 @@
       <c r="A41" s="7">
         <v>2044</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>1218</v>
+      <c r="B41" s="13" t="s">
+        <v>1249</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>723</v>
@@ -29618,8 +29628,8 @@
       <c r="A42" s="7">
         <v>2036</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>1219</v>
+      <c r="B42" s="13" t="s">
+        <v>1250</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>723</v>
@@ -29632,8 +29642,8 @@
       <c r="A43" s="7">
         <v>2034</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>1220</v>
+      <c r="B43" s="13" t="s">
+        <v>1251</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>723</v>
@@ -29646,8 +29656,8 @@
       <c r="A44" s="7">
         <v>2037</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>1221</v>
+      <c r="B44" s="13" t="s">
+        <v>1252</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>723</v>
@@ -29660,8 +29670,8 @@
       <c r="A45" s="7">
         <v>2038</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>1222</v>
+      <c r="B45" s="13" t="s">
+        <v>1253</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>723</v>
@@ -29674,8 +29684,8 @@
       <c r="A46" s="7">
         <v>2039</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>1223</v>
+      <c r="B46" s="13" t="s">
+        <v>1254</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>723</v>
@@ -29688,8 +29698,8 @@
       <c r="A47" s="7">
         <v>2045</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>1224</v>
+      <c r="B47" s="13" t="s">
+        <v>1255</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>723</v>
@@ -37348,88 +37358,88 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1225</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1226</v>
+        <v>1181</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1240</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1227</v>
+        <v>1182</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1241</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1228</v>
+        <v>1183</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1242</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1229</v>
+        <v>1184</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1243</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1230</v>
+        <v>1185</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1244</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1231</v>
+        <v>1186</v>
       </c>
       <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1232</v>
+        <v>1187</v>
       </c>
       <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1233</v>
+        <v>1188</v>
       </c>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>1234</v>
+        <v>1189</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>1235</v>
+        <v>1190</v>
       </c>
       <c r="B11" s="1"/>
     </row>
     <row r="12" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1236</v>
+        <v>1191</v>
       </c>
       <c r="B12" s="1"/>
     </row>
     <row r="13" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>1237</v>
+        <v>1192</v>
       </c>
       <c r="B13" s="1"/>
     </row>
@@ -41401,12 +41411,12 @@
         <v>1080</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1238</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1239</v>
+        <v>1194</v>
       </c>
       <c r="B2" s="9"/>
     </row>
